--- a/shucle_report/검단신도시/20260101_20260325/report_검단신도시_20260101_20260325.xlsx
+++ b/shucle_report/검단신도시/20260101_20260325/report_검단신도시_20260101_20260325.xlsx
@@ -504,7 +504,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>분석기간: 2026.01.01 ~ 03.25 | 비교기간: 2025.10.01 ~ 12.30 | 생성: 2026-03-26 13:09 | 차트: 124개</t>
+          <t>분석기간: 2026.01.01 ~ 03.25 | 비교기간: 2025.10.01 ~ 12.30 | 생성: 2026-03-26 14:48 | 차트: 124개</t>
         </is>
       </c>
     </row>
@@ -1949,17 +1949,17 @@
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>-3.2</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
@@ -1969,7 +1969,7 @@
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>평일 47.7명 (6% 감소)</t>
+          <t>평일 34.1명 (6% 감소)</t>
         </is>
       </c>
     </row>
@@ -1986,17 +1986,17 @@
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>62.0</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>69.1</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>+7.1</t>
+          <t>+2.0</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>주말 69.1명 (11% 증가)</t>
+          <t>주말 19.7명 (11% 증가)</t>
         </is>
       </c>
     </row>
@@ -2178,17 +2178,17 @@
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>8.9</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>평일 11.5분 (8% 감소)</t>
+          <t>평일 8.2분 (8% 감소)</t>
         </is>
       </c>
     </row>
@@ -2215,17 +2215,17 @@
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>+1.6</t>
+          <t>+0.5</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>주말 16.0분 (11% 증가)</t>
+          <t>주말 4.6분 (11% 증가)</t>
         </is>
       </c>
     </row>
@@ -3342,22 +3342,22 @@
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>8,672</t>
+          <t>8,569</t>
         </is>
       </c>
       <c r="E82" s="7" t="inlineStr">
         <is>
-          <t>+625.1</t>
+          <t>+521.8</t>
         </is>
       </c>
       <c r="F82" s="7" t="inlineStr">
         <is>
-          <t>+7.8%</t>
+          <t>+6.5%</t>
         </is>
       </c>
       <c r="G82" s="6" t="inlineStr">
         <is>
-          <t>누적 8672명 (8% 증가)</t>
+          <t>누적 8569명 (6% 증가)</t>
         </is>
       </c>
     </row>
